--- a/docs/app/api/files/results-2.xlsx
+++ b/docs/app/api/files/results-2.xlsx
@@ -516,7 +516,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-04 09:46 UTC · 34 ms</t>
+          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-28 18:35 UTC · 53 ms</t>
         </is>
       </c>
     </row>
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9055648.470000001</v>
+        <v>9055803.439999999</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-6213500.42</v>
+        <v>-2188375.04</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>553.05</v>
+        <v>552.99</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-460.62</v>
+        <v>-103.13</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-1.61</v>
+        <v>-0.36</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -632,11 +632,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.0765</v>
+        <v>-0.0444</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>better</t>
+          <t>worse</t>
         </is>
       </c>
     </row>
@@ -655,11 +655,11 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.0765</v>
+        <v>-0.0444</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>better</t>
+          <t>worse</t>
         </is>
       </c>
     </row>
@@ -678,11 +678,11 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.1135</v>
+        <v>-0.2234</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>better</t>
+          <t>worse</t>
         </is>
       </c>
     </row>
@@ -701,11 +701,11 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.1135</v>
+        <v>0.2234</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>better</t>
+          <t>worse</t>
         </is>
       </c>
     </row>
@@ -724,11 +724,11 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.1259</v>
+        <v>0.0026</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>better</t>
+          <t>worse</t>
         </is>
       </c>
     </row>
@@ -747,11 +747,11 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-29</v>
+        <v>0</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>better</t>
+          <t>flat</t>
         </is>
       </c>
     </row>
@@ -770,11 +770,11 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-19</v>
+        <v>0</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>better</t>
+          <t>flat</t>
         </is>
       </c>
     </row>
@@ -940,23 +940,23 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Port Province</t>
+          <t>National Capital District</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>168000</v>
       </c>
       <c r="E2" t="n">
-        <v>587.554</v>
+        <v>588.05</v>
       </c>
       <c r="F2" t="n">
-        <v>587.554</v>
+        <v>588.05</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>222873.36</v>
+        <v>223034.38</v>
       </c>
       <c r="I2" t="n">
         <v>1.33</v>
@@ -980,7 +980,7 @@
         <v>0.08</v>
       </c>
       <c r="N2" t="n">
-        <v>108.1</v>
+        <v>108</v>
       </c>
       <c r="O2" t="n">
         <v>0.0262</v>
@@ -1024,7 +1024,7 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>177293.09</v>
+        <v>177273.58</v>
       </c>
       <c r="I3" t="n">
         <v>1.34</v>
@@ -1092,7 +1092,7 @@
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>80710.8</v>
+        <v>80701.78999999999</v>
       </c>
       <c r="I4" t="n">
         <v>1.32</v>
@@ -1160,7 +1160,7 @@
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>71788.28999999999</v>
+        <v>71780.3</v>
       </c>
       <c r="I5" t="n">
         <v>1.33</v>
@@ -1228,7 +1228,7 @@
         <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>50891.71</v>
+        <v>50886.09</v>
       </c>
       <c r="I6" t="n">
         <v>1.34</v>
@@ -1296,7 +1296,7 @@
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>71370.98</v>
+        <v>71364.03</v>
       </c>
       <c r="I7" t="n">
         <v>1.52</v>
@@ -1364,7 +1364,7 @@
         <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>72844.02</v>
+        <v>72837.81</v>
       </c>
       <c r="I8" t="n">
         <v>1.73</v>
@@ -1432,7 +1432,7 @@
         <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>33981.84</v>
+        <v>33979.03</v>
       </c>
       <c r="I9" t="n">
         <v>1.79</v>
@@ -1500,7 +1500,7 @@
         <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>63375.83</v>
+        <v>63370.21</v>
       </c>
       <c r="I10" t="n">
         <v>1.67</v>
@@ -1631,7 +1631,7 @@
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>26069.75</v>
+        <v>26067.38</v>
       </c>
       <c r="I12" t="n">
         <v>1.63</v>
@@ -1699,7 +1699,7 @@
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>112612.73</v>
+        <v>112604.16</v>
       </c>
       <c r="I13" t="n">
         <v>1.94</v>
@@ -1767,7 +1767,7 @@
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>38144.73</v>
+        <v>38141.63</v>
       </c>
       <c r="I14" t="n">
         <v>1.82</v>
@@ -1835,7 +1835,7 @@
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>58125.31</v>
+        <v>58120.58</v>
       </c>
       <c r="I15" t="n">
         <v>1.82</v>
@@ -1903,7 +1903,7 @@
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>32695.49</v>
+        <v>32692.82</v>
       </c>
       <c r="I16" t="n">
         <v>1.82</v>
@@ -1971,7 +1971,7 @@
         <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>47377.8</v>
+        <v>47374.26</v>
       </c>
       <c r="I17" t="n">
         <v>1.97</v>
@@ -2102,7 +2102,7 @@
         <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>83242.39999999999</v>
+        <v>83235.89</v>
       </c>
       <c r="I19" t="n">
         <v>1.89</v>
@@ -2170,7 +2170,7 @@
         <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>71582.00999999999</v>
+        <v>71576.24000000001</v>
       </c>
       <c r="I20" t="n">
         <v>1.84</v>
@@ -2238,7 +2238,7 @@
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>51392.21</v>
+        <v>51388.07</v>
       </c>
       <c r="I21" t="n">
         <v>1.84</v>
@@ -2306,7 +2306,7 @@
         <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>56898.52</v>
+        <v>56893.94</v>
       </c>
       <c r="I22" t="n">
         <v>1.84</v>
@@ -2500,7 +2500,7 @@
         <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>13765.77</v>
+        <v>13764.66</v>
       </c>
       <c r="I25" t="n">
         <v>1.84</v>
@@ -2568,7 +2568,7 @@
         <v>1</v>
       </c>
       <c r="H26" t="n">
-        <v>110629.04</v>
+        <v>110619.88</v>
       </c>
       <c r="I26" t="n">
         <v>1.78</v>
@@ -2620,7 +2620,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Losuia Province</t>
+          <t>Milne Bay</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -2636,7 +2636,7 @@
         <v>1</v>
       </c>
       <c r="H27" t="n">
-        <v>104130.74</v>
+        <v>104126.46</v>
       </c>
       <c r="I27" t="n">
         <v>3.59</v>
@@ -2704,7 +2704,7 @@
         <v>1</v>
       </c>
       <c r="H28" t="n">
-        <v>75405.02</v>
+        <v>75401.92</v>
       </c>
       <c r="I28" t="n">
         <v>3.59</v>
@@ -2772,7 +2772,7 @@
         <v>1</v>
       </c>
       <c r="H29" t="n">
-        <v>86177.17</v>
+        <v>86173.62</v>
       </c>
       <c r="I29" t="n">
         <v>3.59</v>
@@ -2840,7 +2840,7 @@
         <v>1</v>
       </c>
       <c r="H30" t="n">
-        <v>50270.01</v>
+        <v>50267.94</v>
       </c>
       <c r="I30" t="n">
         <v>3.59</v>
@@ -2908,7 +2908,7 @@
         <v>1</v>
       </c>
       <c r="H31" t="n">
-        <v>30333.77</v>
+        <v>30331.26</v>
       </c>
       <c r="I31" t="n">
         <v>1.78</v>
@@ -2976,7 +2976,7 @@
         <v>1</v>
       </c>
       <c r="H32" t="n">
-        <v>53860.73</v>
+        <v>53858.51</v>
       </c>
       <c r="I32" t="n">
         <v>3.59</v>
@@ -3044,7 +3044,7 @@
         <v>1</v>
       </c>
       <c r="H33" t="n">
-        <v>141024.19</v>
+        <v>141013.69</v>
       </c>
       <c r="I33" t="n">
         <v>1.99</v>
@@ -3112,7 +3112,7 @@
         <v>1</v>
       </c>
       <c r="H34" t="n">
-        <v>43697.63</v>
+        <v>43694.38</v>
       </c>
       <c r="I34" t="n">
         <v>1.99</v>
@@ -3180,7 +3180,7 @@
         <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>25821.33</v>
+        <v>25819.41</v>
       </c>
       <c r="I35" t="n">
         <v>1.99</v>
@@ -3311,7 +3311,7 @@
         <v>1</v>
       </c>
       <c r="H37" t="n">
-        <v>21848.82</v>
+        <v>21847.19</v>
       </c>
       <c r="I37" t="n">
         <v>1.99</v>
@@ -3379,7 +3379,7 @@
         <v>1</v>
       </c>
       <c r="H38" t="n">
-        <v>27807.59</v>
+        <v>27805.52</v>
       </c>
       <c r="I38" t="n">
         <v>1.99</v>
@@ -3431,23 +3431,23 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Angau Province</t>
+          <t>Morobe</t>
         </is>
       </c>
       <c r="D39" t="n">
         <v>188000</v>
       </c>
       <c r="E39" t="n">
-        <v>656.3200000000001</v>
+        <v>658.056</v>
       </c>
       <c r="F39" t="n">
-        <v>656.3200000000001</v>
+        <v>658.056</v>
       </c>
       <c r="G39" t="n">
         <v>1</v>
       </c>
       <c r="H39" t="n">
-        <v>281596.32</v>
+        <v>282305.35</v>
       </c>
       <c r="I39" t="n">
         <v>1.5</v>
@@ -3471,7 +3471,7 @@
         <v>0.08</v>
       </c>
       <c r="N39" t="n">
-        <v>108.3</v>
+        <v>108</v>
       </c>
       <c r="O39" t="n">
         <v>0.0252</v>
@@ -3515,7 +3515,7 @@
         <v>1</v>
       </c>
       <c r="H40" t="n">
-        <v>91940.23</v>
+        <v>91932.25</v>
       </c>
       <c r="I40" t="n">
         <v>1.7</v>
@@ -3583,7 +3583,7 @@
         <v>1</v>
       </c>
       <c r="H41" t="n">
-        <v>55257</v>
+        <v>55252.42</v>
       </c>
       <c r="I41" t="n">
         <v>1.78</v>
@@ -3651,7 +3651,7 @@
         <v>1</v>
       </c>
       <c r="H42" t="n">
-        <v>81308.21000000001</v>
+        <v>81302.00999999999</v>
       </c>
       <c r="I42" t="n">
         <v>1.94</v>
@@ -3719,7 +3719,7 @@
         <v>1</v>
       </c>
       <c r="H43" t="n">
-        <v>70146.7</v>
+        <v>70141.38</v>
       </c>
       <c r="I43" t="n">
         <v>1.95</v>
@@ -3850,7 +3850,7 @@
         <v>1</v>
       </c>
       <c r="H45" t="n">
-        <v>32910.47</v>
+        <v>32907.95</v>
       </c>
       <c r="I45" t="n">
         <v>1.94</v>
@@ -3918,7 +3918,7 @@
         <v>1</v>
       </c>
       <c r="H46" t="n">
-        <v>38675.28</v>
+        <v>38671.88</v>
       </c>
       <c r="I46" t="n">
         <v>1.68</v>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Modilon Province</t>
+          <t>Madang</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -3986,7 +3986,7 @@
         <v>1</v>
       </c>
       <c r="H47" t="n">
-        <v>154817.2</v>
+        <v>154803.01</v>
       </c>
       <c r="I47" t="n">
         <v>1.61</v>
@@ -4054,7 +4054,7 @@
         <v>1</v>
       </c>
       <c r="H48" t="n">
-        <v>85906.72</v>
+        <v>85900.66</v>
       </c>
       <c r="I48" t="n">
         <v>2.1</v>
@@ -4122,7 +4122,7 @@
         <v>1</v>
       </c>
       <c r="H49" t="n">
-        <v>58833.75</v>
+        <v>58829.91</v>
       </c>
       <c r="I49" t="n">
         <v>2.26</v>
@@ -4190,7 +4190,7 @@
         <v>1</v>
       </c>
       <c r="H50" t="n">
-        <v>47559.03</v>
+        <v>47555.78</v>
       </c>
       <c r="I50" t="n">
         <v>2.16</v>
@@ -4258,7 +4258,7 @@
         <v>1</v>
       </c>
       <c r="H51" t="n">
-        <v>54158.2</v>
+        <v>54154.06</v>
       </c>
       <c r="I51" t="n">
         <v>1.93</v>
@@ -4452,7 +4452,7 @@
         <v>1</v>
       </c>
       <c r="H54" t="n">
-        <v>188312.22</v>
+        <v>188299.21</v>
       </c>
       <c r="I54" t="n">
         <v>2.14</v>
@@ -4520,7 +4520,7 @@
         <v>1</v>
       </c>
       <c r="H55" t="n">
-        <v>111275.4</v>
+        <v>111267.72</v>
       </c>
       <c r="I55" t="n">
         <v>2.14</v>
@@ -4588,7 +4588,7 @@
         <v>1</v>
       </c>
       <c r="H56" t="n">
-        <v>94156.11</v>
+        <v>94149.61</v>
       </c>
       <c r="I56" t="n">
         <v>2.14</v>
@@ -4656,7 +4656,7 @@
         <v>1</v>
       </c>
       <c r="H57" t="n">
-        <v>66717.24000000001</v>
+        <v>66713.7</v>
       </c>
       <c r="I57" t="n">
         <v>2.78</v>
@@ -4724,7 +4724,7 @@
         <v>1</v>
       </c>
       <c r="H58" t="n">
-        <v>70617.08</v>
+        <v>70612.2</v>
       </c>
       <c r="I58" t="n">
         <v>2.14</v>
@@ -4792,7 +4792,7 @@
         <v>1</v>
       </c>
       <c r="H59" t="n">
-        <v>57777.61</v>
+        <v>57773.62</v>
       </c>
       <c r="I59" t="n">
         <v>2.14</v>
@@ -4860,7 +4860,7 @@
         <v>1</v>
       </c>
       <c r="H60" t="n">
-        <v>41698.28</v>
+        <v>41696.06</v>
       </c>
       <c r="I60" t="n">
         <v>2.78</v>
@@ -4928,7 +4928,7 @@
         <v>1</v>
       </c>
       <c r="H61" t="n">
-        <v>100575.85</v>
+        <v>100568.9</v>
       </c>
       <c r="I61" t="n">
         <v>2.14</v>
@@ -4996,7 +4996,7 @@
         <v>1</v>
       </c>
       <c r="H62" t="n">
-        <v>83456.55</v>
+        <v>83450.78999999999</v>
       </c>
       <c r="I62" t="n">
         <v>2.14</v>
@@ -5064,7 +5064,7 @@
         <v>1</v>
       </c>
       <c r="H63" t="n">
-        <v>51357.88</v>
+        <v>51354.33</v>
       </c>
       <c r="I63" t="n">
         <v>2.14</v>
@@ -5132,7 +5132,7 @@
         <v>1</v>
       </c>
       <c r="H64" t="n">
-        <v>47078.06</v>
+        <v>47074.8</v>
       </c>
       <c r="I64" t="n">
         <v>2.14</v>
@@ -5389,7 +5389,7 @@
         <v>1</v>
       </c>
       <c r="H68" t="n">
-        <v>132797.63</v>
+        <v>132786.84</v>
       </c>
       <c r="I68" t="n">
         <v>1.84</v>
@@ -5457,7 +5457,7 @@
         <v>1</v>
       </c>
       <c r="H69" t="n">
-        <v>85006.3</v>
+        <v>84999.11</v>
       </c>
       <c r="I69" t="n">
         <v>1.77</v>
@@ -5525,7 +5525,7 @@
         <v>1</v>
       </c>
       <c r="H70" t="n">
-        <v>75399.53</v>
+        <v>75393.84</v>
       </c>
       <c r="I70" t="n">
         <v>1.98</v>
@@ -5593,7 +5593,7 @@
         <v>1</v>
       </c>
       <c r="H71" t="n">
-        <v>86519.28</v>
+        <v>86513.14</v>
       </c>
       <c r="I71" t="n">
         <v>2.11</v>
@@ -5661,7 +5661,7 @@
         <v>1</v>
       </c>
       <c r="H72" t="n">
-        <v>54439.61</v>
+        <v>54435.26</v>
       </c>
       <c r="I72" t="n">
         <v>1.88</v>
@@ -5729,7 +5729,7 @@
         <v>1</v>
       </c>
       <c r="H73" t="n">
-        <v>61750.56</v>
+        <v>61745.77</v>
       </c>
       <c r="I73" t="n">
         <v>1.93</v>
@@ -5797,7 +5797,7 @@
         <v>1</v>
       </c>
       <c r="H74" t="n">
-        <v>181241.13</v>
+        <v>181228.55</v>
       </c>
       <c r="I74" t="n">
         <v>2.16</v>
@@ -5865,7 +5865,7 @@
         <v>1</v>
       </c>
       <c r="H75" t="n">
-        <v>96690.69</v>
+        <v>96684.25</v>
       </c>
       <c r="I75" t="n">
         <v>2.25</v>
@@ -5933,7 +5933,7 @@
         <v>1</v>
       </c>
       <c r="H76" t="n">
-        <v>68282.11</v>
+        <v>68277.46000000001</v>
       </c>
       <c r="I76" t="n">
         <v>2.2</v>
@@ -6001,7 +6001,7 @@
         <v>1</v>
       </c>
       <c r="H77" t="n">
-        <v>55632.18</v>
+        <v>55628.13</v>
       </c>
       <c r="I77" t="n">
         <v>2.06</v>
@@ -6132,7 +6132,7 @@
         <v>1</v>
       </c>
       <c r="H79" t="n">
-        <v>146284.01</v>
+        <v>146272.18</v>
       </c>
       <c r="I79" t="n">
         <v>1.85</v>
@@ -6200,7 +6200,7 @@
         <v>1</v>
       </c>
       <c r="H80" t="n">
-        <v>79234</v>
+        <v>79227.41</v>
       </c>
       <c r="I80" t="n">
         <v>1.8</v>
@@ -6268,7 +6268,7 @@
         <v>1</v>
       </c>
       <c r="H81" t="n">
-        <v>68591.00999999999</v>
+        <v>68585.61</v>
       </c>
       <c r="I81" t="n">
         <v>1.91</v>
@@ -6336,7 +6336,7 @@
         <v>1</v>
       </c>
       <c r="H82" t="n">
-        <v>77510.98</v>
+        <v>77505.14</v>
       </c>
       <c r="I82" t="n">
         <v>1.99</v>
@@ -6404,7 +6404,7 @@
         <v>1</v>
       </c>
       <c r="H83" t="n">
-        <v>45340.67</v>
+        <v>45337.22</v>
       </c>
       <c r="I83" t="n">
         <v>1.97</v>
@@ -6472,7 +6472,7 @@
         <v>1</v>
       </c>
       <c r="H84" t="n">
-        <v>51631.88</v>
+        <v>51627.69</v>
       </c>
       <c r="I84" t="n">
         <v>1.84</v>
@@ -6540,7 +6540,7 @@
         <v>1</v>
       </c>
       <c r="H85" t="n">
-        <v>182508.05</v>
+        <v>182491.27</v>
       </c>
       <c r="I85" t="n">
         <v>1.63</v>
@@ -6608,7 +6608,7 @@
         <v>1</v>
       </c>
       <c r="H86" t="n">
-        <v>59706.84</v>
+        <v>59701.75</v>
       </c>
       <c r="I86" t="n">
         <v>1.76</v>
@@ -6676,7 +6676,7 @@
         <v>1</v>
       </c>
       <c r="H87" t="n">
-        <v>54923.73</v>
+        <v>54919.08</v>
       </c>
       <c r="I87" t="n">
         <v>1.77</v>
@@ -6744,7 +6744,7 @@
         <v>1</v>
       </c>
       <c r="H88" t="n">
-        <v>37666.8</v>
+        <v>37663.51</v>
       </c>
       <c r="I88" t="n">
         <v>1.71</v>
@@ -6812,7 +6812,7 @@
         <v>1</v>
       </c>
       <c r="H89" t="n">
-        <v>43681.16</v>
+        <v>43677.26</v>
       </c>
       <c r="I89" t="n">
         <v>1.68</v>
@@ -6880,7 +6880,7 @@
         <v>1</v>
       </c>
       <c r="H90" t="n">
-        <v>102912.92</v>
+        <v>102904.23</v>
       </c>
       <c r="I90" t="n">
         <v>1.77</v>
@@ -6948,7 +6948,7 @@
         <v>1</v>
       </c>
       <c r="H91" t="n">
-        <v>72079.28</v>
+        <v>72073.14</v>
       </c>
       <c r="I91" t="n">
         <v>1.76</v>
@@ -7016,7 +7016,7 @@
         <v>1</v>
       </c>
       <c r="H92" t="n">
-        <v>82045.24000000001</v>
+        <v>82038.2</v>
       </c>
       <c r="I92" t="n">
         <v>1.75</v>
@@ -7084,7 +7084,7 @@
         <v>1</v>
       </c>
       <c r="H93" t="n">
-        <v>44254.4</v>
+        <v>44250.81</v>
       </c>
       <c r="I93" t="n">
         <v>1.84</v>
@@ -7215,7 +7215,7 @@
         <v>1</v>
       </c>
       <c r="H95" t="n">
-        <v>139309.46</v>
+        <v>139298.38</v>
       </c>
       <c r="I95" t="n">
         <v>1.88</v>
@@ -7283,7 +7283,7 @@
         <v>1</v>
       </c>
       <c r="H96" t="n">
-        <v>83935.56</v>
+        <v>83928.67</v>
       </c>
       <c r="I96" t="n">
         <v>1.82</v>
@@ -7351,7 +7351,7 @@
         <v>1</v>
       </c>
       <c r="H97" t="n">
-        <v>63406.62</v>
+        <v>63401.67</v>
       </c>
       <c r="I97" t="n">
         <v>1.92</v>
@@ -7482,7 +7482,7 @@
         <v>1</v>
       </c>
       <c r="H99" t="n">
-        <v>56332.31</v>
+        <v>56327.96</v>
       </c>
       <c r="I99" t="n">
         <v>1.94</v>
@@ -7550,7 +7550,7 @@
         <v>1</v>
       </c>
       <c r="H100" t="n">
-        <v>48945.09</v>
+        <v>48941.35</v>
       </c>
       <c r="I100" t="n">
         <v>1.96</v>
@@ -7597,28 +7597,28 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Goroka Base Hospital</t>
+          <t>Goroka Provincial Hospital</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Goroka Province</t>
+          <t>Eastern Highlands</t>
         </is>
       </c>
       <c r="D101" t="n">
         <v>108000</v>
       </c>
       <c r="E101" t="n">
-        <v>378.156</v>
+        <v>378.032</v>
       </c>
       <c r="F101" t="n">
-        <v>378.156</v>
+        <v>378.032</v>
       </c>
       <c r="G101" t="n">
         <v>1</v>
       </c>
       <c r="H101" t="n">
-        <v>226040.27</v>
+        <v>225950.76</v>
       </c>
       <c r="I101" t="n">
         <v>2.09</v>
@@ -7686,7 +7686,7 @@
         <v>1</v>
       </c>
       <c r="H102" t="n">
-        <v>118672.29</v>
+        <v>118663.12</v>
       </c>
       <c r="I102" t="n">
         <v>1.91</v>
@@ -7754,7 +7754,7 @@
         <v>1</v>
       </c>
       <c r="H103" t="n">
-        <v>71390.34</v>
+        <v>71385.32000000001</v>
       </c>
       <c r="I103" t="n">
         <v>2.1</v>
@@ -7822,7 +7822,7 @@
         <v>1</v>
       </c>
       <c r="H104" t="n">
-        <v>69783.44</v>
+        <v>69778.86</v>
       </c>
       <c r="I104" t="n">
         <v>2.25</v>
@@ -7890,7 +7890,7 @@
         <v>1</v>
       </c>
       <c r="H105" t="n">
-        <v>59081.27</v>
+        <v>59077.13</v>
       </c>
       <c r="I105" t="n">
         <v>2.11</v>
@@ -8084,7 +8084,7 @@
         <v>1</v>
       </c>
       <c r="H108" t="n">
-        <v>95558.89</v>
+        <v>95553.87</v>
       </c>
       <c r="I108" t="n">
         <v>2.81</v>
@@ -8152,7 +8152,7 @@
         <v>1</v>
       </c>
       <c r="H109" t="n">
-        <v>25295</v>
+        <v>25293.67</v>
       </c>
       <c r="I109" t="n">
         <v>2.81</v>
@@ -8220,7 +8220,7 @@
         <v>1</v>
       </c>
       <c r="H110" t="n">
-        <v>18268.61</v>
+        <v>18267.65</v>
       </c>
       <c r="I110" t="n">
         <v>2.81</v>
@@ -8288,7 +8288,7 @@
         <v>1</v>
       </c>
       <c r="H111" t="n">
-        <v>15458.06</v>
+        <v>15457.24</v>
       </c>
       <c r="I111" t="n">
         <v>2.81</v>
@@ -8356,7 +8356,7 @@
         <v>1</v>
       </c>
       <c r="H112" t="n">
-        <v>14052.78</v>
+        <v>14052.04</v>
       </c>
       <c r="I112" t="n">
         <v>2.81</v>
@@ -8408,7 +8408,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Kavieng Province</t>
+          <t>New Ireland</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -8424,7 +8424,7 @@
         <v>1</v>
       </c>
       <c r="H113" t="n">
-        <v>130105.04</v>
+        <v>130096.46</v>
       </c>
       <c r="I113" t="n">
         <v>2.24</v>
@@ -8492,7 +8492,7 @@
         <v>1</v>
       </c>
       <c r="H114" t="n">
-        <v>103186.75</v>
+        <v>103179.95</v>
       </c>
       <c r="I114" t="n">
         <v>2.24</v>
@@ -8560,7 +8560,7 @@
         <v>1</v>
       </c>
       <c r="H115" t="n">
-        <v>44451.39</v>
+        <v>44448.58</v>
       </c>
       <c r="I115" t="n">
         <v>2.34</v>
@@ -8628,7 +8628,7 @@
         <v>1</v>
       </c>
       <c r="H116" t="n">
-        <v>38134.23</v>
+        <v>38131.72</v>
       </c>
       <c r="I116" t="n">
         <v>2.24</v>
@@ -8696,7 +8696,7 @@
         <v>1</v>
       </c>
       <c r="H117" t="n">
-        <v>18716.37</v>
+        <v>18715.19</v>
       </c>
       <c r="I117" t="n">
         <v>2.34</v>
@@ -8764,7 +8764,7 @@
         <v>1</v>
       </c>
       <c r="H118" t="n">
-        <v>32753.66</v>
+        <v>32751.59</v>
       </c>
       <c r="I118" t="n">
         <v>2.34</v>
@@ -8832,7 +8832,7 @@
         <v>1</v>
       </c>
       <c r="H119" t="n">
-        <v>164175.34</v>
+        <v>164161.74</v>
       </c>
       <c r="I119" t="n">
         <v>1.78</v>
@@ -8900,7 +8900,7 @@
         <v>1</v>
       </c>
       <c r="H120" t="n">
-        <v>105051.16</v>
+        <v>105042.15</v>
       </c>
       <c r="I120" t="n">
         <v>1.72</v>
@@ -8968,7 +8968,7 @@
         <v>1</v>
       </c>
       <c r="H121" t="n">
-        <v>68164.31</v>
+        <v>68158.7</v>
       </c>
       <c r="I121" t="n">
         <v>1.79</v>
@@ -9036,7 +9036,7 @@
         <v>1</v>
       </c>
       <c r="H122" t="n">
-        <v>37025.65</v>
+        <v>37022.55</v>
       </c>
       <c r="I122" t="n">
         <v>1.76</v>
@@ -9104,7 +9104,7 @@
         <v>1</v>
       </c>
       <c r="H123" t="n">
-        <v>54638.48</v>
+        <v>54635.08</v>
       </c>
       <c r="I123" t="n">
         <v>2.38</v>
@@ -9172,7 +9172,7 @@
         <v>1</v>
       </c>
       <c r="H124" t="n">
-        <v>42760.55</v>
+        <v>42757.89</v>
       </c>
       <c r="I124" t="n">
         <v>2.38</v>
@@ -9240,7 +9240,7 @@
         <v>1</v>
       </c>
       <c r="H125" t="n">
-        <v>166557.33</v>
+        <v>166545.8</v>
       </c>
       <c r="I125" t="n">
         <v>2.14</v>
@@ -9308,7 +9308,7 @@
         <v>1</v>
       </c>
       <c r="H126" t="n">
-        <v>68331.21000000001</v>
+        <v>68326.48</v>
       </c>
       <c r="I126" t="n">
         <v>2.14</v>
@@ -9376,7 +9376,7 @@
         <v>1</v>
       </c>
       <c r="H127" t="n">
-        <v>35418.56</v>
+        <v>35416.2</v>
       </c>
       <c r="I127" t="n">
         <v>2.21</v>
@@ -9444,7 +9444,7 @@
         <v>1</v>
       </c>
       <c r="H128" t="n">
-        <v>87549.37</v>
+        <v>87543.31</v>
       </c>
       <c r="I128" t="n">
         <v>2.14</v>
@@ -9512,7 +9512,7 @@
         <v>1</v>
       </c>
       <c r="H129" t="n">
-        <v>53127.85</v>
+        <v>53124.3</v>
       </c>
       <c r="I129" t="n">
         <v>2.21</v>
@@ -9580,7 +9580,7 @@
         <v>1</v>
       </c>
       <c r="H130" t="n">
-        <v>157537.74</v>
+        <v>157527.84</v>
       </c>
       <c r="I130" t="n">
         <v>2.35</v>
@@ -9648,7 +9648,7 @@
         <v>1</v>
       </c>
       <c r="H131" t="n">
-        <v>122268.1</v>
+        <v>122260.41</v>
       </c>
       <c r="I131" t="n">
         <v>2.35</v>
@@ -9716,7 +9716,7 @@
         <v>1</v>
       </c>
       <c r="H132" t="n">
-        <v>103457.62</v>
+        <v>103451.12</v>
       </c>
       <c r="I132" t="n">
         <v>2.35</v>
@@ -9784,7 +9784,7 @@
         <v>1</v>
       </c>
       <c r="H133" t="n">
-        <v>42323.57</v>
+        <v>42320.91</v>
       </c>
       <c r="I133" t="n">
         <v>2.35</v>
@@ -9852,7 +9852,7 @@
         <v>1</v>
       </c>
       <c r="H134" t="n">
-        <v>16459.17</v>
+        <v>16458.13</v>
       </c>
       <c r="I134" t="n">
         <v>2.35</v>
@@ -9920,7 +9920,7 @@
         <v>1</v>
       </c>
       <c r="H135" t="n">
-        <v>37620.95</v>
+        <v>37618.59</v>
       </c>
       <c r="I135" t="n">
         <v>2.35</v>
@@ -10099,7 +10099,7 @@
         <v>195.25</v>
       </c>
       <c r="I2" t="n">
-        <v>14351.99</v>
+        <v>14351.95</v>
       </c>
       <c r="J2" t="n">
         <v>322.81</v>
@@ -10157,7 +10157,7 @@
         <v>195.25</v>
       </c>
       <c r="I3" t="n">
-        <v>21869.71</v>
+        <v>21869.64</v>
       </c>
       <c r="J3" t="n">
         <v>483.47</v>
@@ -10215,7 +10215,7 @@
         <v>195.25</v>
       </c>
       <c r="I4" t="n">
-        <v>12301.71</v>
+        <v>12301.67</v>
       </c>
       <c r="J4" t="n">
         <v>416.21</v>
@@ -10273,7 +10273,7 @@
         <v>216.81</v>
       </c>
       <c r="I5" t="n">
-        <v>33390.95</v>
+        <v>33390.86</v>
       </c>
       <c r="J5" t="n">
         <v>538.08</v>
@@ -10331,7 +10331,7 @@
         <v>200.68</v>
       </c>
       <c r="I6" t="n">
-        <v>27395.49</v>
+        <v>27395.41</v>
       </c>
       <c r="J6" t="n">
         <v>1162.1</v>
@@ -10389,7 +10389,7 @@
         <v>200.68</v>
       </c>
       <c r="I7" t="n">
-        <v>19668.56</v>
+        <v>19668.5</v>
       </c>
       <c r="J7" t="n">
         <v>1251.46</v>
@@ -10447,7 +10447,7 @@
         <v>200.68</v>
       </c>
       <c r="I8" t="n">
-        <v>21775.9</v>
+        <v>21775.84</v>
       </c>
       <c r="J8" t="n">
         <v>767.52</v>
@@ -10505,7 +10505,7 @@
         <v>200.68</v>
       </c>
       <c r="I9" t="n">
-        <v>5268.36</v>
+        <v>5268.35</v>
       </c>
       <c r="J9" t="n">
         <v>955.4400000000001</v>
@@ -10563,7 +10563,7 @@
         <v>186.08</v>
       </c>
       <c r="I10" t="n">
-        <v>40383.81</v>
+        <v>40383.69</v>
       </c>
       <c r="J10" t="n">
         <v>448.61</v>
@@ -10621,7 +10621,7 @@
         <v>186.08</v>
       </c>
       <c r="I11" t="n">
-        <v>11072.98</v>
+        <v>11072.95</v>
       </c>
       <c r="J11" t="n">
         <v>358.09</v>
@@ -10679,7 +10679,7 @@
         <v>702.15</v>
       </c>
       <c r="I12" t="n">
-        <v>71274.10000000001</v>
+        <v>71274.05</v>
       </c>
       <c r="J12" t="n">
         <v>534.23</v>
@@ -10737,7 +10737,7 @@
         <v>702.15</v>
       </c>
       <c r="I13" t="n">
-        <v>51612.28</v>
+        <v>51612.24</v>
       </c>
       <c r="J13" t="n">
         <v>758.5700000000001</v>
@@ -10795,7 +10795,7 @@
         <v>702.15</v>
       </c>
       <c r="I14" t="n">
-        <v>58985.47</v>
+        <v>58985.42</v>
       </c>
       <c r="J14" t="n">
         <v>483.91</v>
@@ -10853,7 +10853,7 @@
         <v>702.15</v>
       </c>
       <c r="I15" t="n">
-        <v>34408.19</v>
+        <v>34408.16</v>
       </c>
       <c r="J15" t="n">
         <v>488.03</v>
@@ -10911,7 +10911,7 @@
         <v>702.15</v>
       </c>
       <c r="I16" t="n">
-        <v>36865.92</v>
+        <v>36865.89</v>
       </c>
       <c r="J16" t="n">
         <v>407.1</v>
@@ -10969,7 +10969,7 @@
         <v>243.77</v>
       </c>
       <c r="I17" t="n">
-        <v>60582.07</v>
+        <v>60581.93</v>
       </c>
       <c r="J17" t="n">
         <v>323.36</v>
@@ -11027,7 +11027,7 @@
         <v>243.77</v>
       </c>
       <c r="I18" t="n">
-        <v>18771.91</v>
+        <v>18771.86</v>
       </c>
       <c r="J18" t="n">
         <v>308.79</v>
@@ -11085,7 +11085,7 @@
         <v>243.77</v>
       </c>
       <c r="I19" t="n">
-        <v>11092.49</v>
+        <v>11092.47</v>
       </c>
       <c r="J19" t="n">
         <v>447.3</v>
@@ -11143,7 +11143,7 @@
         <v>243.77</v>
       </c>
       <c r="I20" t="n">
-        <v>9385.950000000001</v>
+        <v>9385.93</v>
       </c>
       <c r="J20" t="n">
         <v>459</v>
@@ -11201,7 +11201,7 @@
         <v>243.77</v>
       </c>
       <c r="I21" t="n">
-        <v>11945.76</v>
+        <v>11945.73</v>
       </c>
       <c r="J21" t="n">
         <v>306.91</v>
@@ -11259,7 +11259,7 @@
         <v>229.39</v>
       </c>
       <c r="I22" t="n">
-        <v>33722.74</v>
+        <v>33722.65</v>
       </c>
       <c r="J22" t="n">
         <v>117.11</v>
@@ -11317,7 +11317,7 @@
         <v>229.39</v>
       </c>
       <c r="I23" t="n">
-        <v>13649.68</v>
+        <v>13649.65</v>
       </c>
       <c r="J23" t="n">
         <v>106.12</v>
@@ -11375,7 +11375,7 @@
         <v>322.79</v>
       </c>
       <c r="I24" t="n">
-        <v>29376.07</v>
+        <v>29376.02</v>
       </c>
       <c r="J24" t="n">
         <v>106.06</v>
@@ -11433,7 +11433,7 @@
         <v>293.91</v>
       </c>
       <c r="I25" t="n">
-        <v>22633.3</v>
+        <v>22633.26</v>
       </c>
       <c r="J25" t="n">
         <v>80.93000000000001</v>
@@ -11491,7 +11491,7 @@
         <v>287.67</v>
       </c>
       <c r="I26" t="n">
-        <v>88609.32000000001</v>
+        <v>88609.14</v>
       </c>
       <c r="J26" t="n">
         <v>364.01</v>
@@ -11549,7 +11549,7 @@
         <v>287.67</v>
       </c>
       <c r="I27" t="n">
-        <v>52360.05</v>
+        <v>52359.95</v>
       </c>
       <c r="J27" t="n">
         <v>428.56</v>
@@ -11607,7 +11607,7 @@
         <v>287.67</v>
       </c>
       <c r="I28" t="n">
-        <v>44304.66</v>
+        <v>44304.57</v>
       </c>
       <c r="J28" t="n">
         <v>280.66</v>
@@ -11665,7 +11665,7 @@
         <v>287.67</v>
       </c>
       <c r="I29" t="n">
-        <v>33228.49</v>
+        <v>33228.43</v>
       </c>
       <c r="J29" t="n">
         <v>390.59</v>
@@ -11723,7 +11723,7 @@
         <v>287.67</v>
       </c>
       <c r="I30" t="n">
-        <v>27186.95</v>
+        <v>27186.9</v>
       </c>
       <c r="J30" t="n">
         <v>405.44</v>
@@ -11781,7 +11781,7 @@
         <v>287.67</v>
       </c>
       <c r="I31" t="n">
-        <v>47325.43</v>
+        <v>47325.34</v>
       </c>
       <c r="J31" t="n">
         <v>698.29</v>
@@ -11839,7 +11839,7 @@
         <v>287.67</v>
       </c>
       <c r="I32" t="n">
-        <v>39270.04</v>
+        <v>39269.96</v>
       </c>
       <c r="J32" t="n">
         <v>544.61</v>
@@ -11897,7 +11897,7 @@
         <v>287.67</v>
       </c>
       <c r="I33" t="n">
-        <v>24166.18</v>
+        <v>24166.13</v>
       </c>
       <c r="J33" t="n">
         <v>560.1</v>
@@ -11955,7 +11955,7 @@
         <v>287.67</v>
       </c>
       <c r="I34" t="n">
-        <v>22152.33</v>
+        <v>22152.29</v>
       </c>
       <c r="J34" t="n">
         <v>494.37</v>
@@ -12013,7 +12013,7 @@
         <v>470.5</v>
       </c>
       <c r="I35" t="n">
-        <v>39525.54</v>
+        <v>39525.49</v>
       </c>
       <c r="J35" t="n">
         <v>532.85</v>
@@ -12071,7 +12071,7 @@
         <v>470.5</v>
       </c>
       <c r="I36" t="n">
-        <v>24703.46</v>
+        <v>24703.43</v>
       </c>
       <c r="J36" t="n">
         <v>426.83</v>
@@ -12129,7 +12129,7 @@
         <v>479.26</v>
       </c>
       <c r="I37" t="n">
-        <v>57037.32</v>
+        <v>57037.25</v>
       </c>
       <c r="J37" t="n">
         <v>477.86</v>
@@ -12187,7 +12187,7 @@
         <v>479.26</v>
       </c>
       <c r="I38" t="n">
-        <v>15098.11</v>
+        <v>15098.1</v>
       </c>
       <c r="J38" t="n">
         <v>482.12</v>
@@ -12245,7 +12245,7 @@
         <v>479.26</v>
       </c>
       <c r="I39" t="n">
-        <v>10904.19</v>
+        <v>10904.18</v>
       </c>
       <c r="J39" t="n">
         <v>480.24</v>
@@ -12303,7 +12303,7 @@
         <v>479.26</v>
       </c>
       <c r="I40" t="n">
-        <v>9226.620000000001</v>
+        <v>9226.610000000001</v>
       </c>
       <c r="J40" t="n">
         <v>481.26</v>
@@ -12361,7 +12361,7 @@
         <v>479.26</v>
       </c>
       <c r="I41" t="n">
-        <v>8387.84</v>
+        <v>8387.83</v>
       </c>
       <c r="J41" t="n">
         <v>412.79</v>
@@ -12419,7 +12419,7 @@
         <v>317.17</v>
       </c>
       <c r="I42" t="n">
-        <v>64391.76</v>
+        <v>64391.64</v>
       </c>
       <c r="J42" t="n">
         <v>311.37</v>
@@ -12477,7 +12477,7 @@
         <v>317.17</v>
       </c>
       <c r="I43" t="n">
-        <v>51069.33</v>
+        <v>51069.23</v>
       </c>
       <c r="J43" t="n">
         <v>94.95999999999999</v>
@@ -12535,7 +12535,7 @@
         <v>344.7</v>
       </c>
       <c r="I44" t="n">
-        <v>22924.63</v>
+        <v>22924.59</v>
       </c>
       <c r="J44" t="n">
         <v>182.8</v>
@@ -12593,7 +12593,7 @@
         <v>317.17</v>
       </c>
       <c r="I45" t="n">
-        <v>18873.45</v>
+        <v>18873.41</v>
       </c>
       <c r="J45" t="n">
         <v>175.95</v>
@@ -12651,7 +12651,7 @@
         <v>344.7</v>
       </c>
       <c r="I46" t="n">
-        <v>9652.469999999999</v>
+        <v>9652.459999999999</v>
       </c>
       <c r="J46" t="n">
         <v>205.12</v>
@@ -12709,7 +12709,7 @@
         <v>344.7</v>
       </c>
       <c r="I47" t="n">
-        <v>16891.83</v>
+        <v>16891.8</v>
       </c>
       <c r="J47" t="n">
         <v>368.78</v>
@@ -12767,7 +12767,7 @@
         <v>355</v>
       </c>
       <c r="I48" t="n">
-        <v>28579.76</v>
+        <v>28579.72</v>
       </c>
       <c r="J48" t="n">
         <v>240.83</v>
@@ -12825,7 +12825,7 @@
         <v>355</v>
       </c>
       <c r="I49" t="n">
-        <v>22366.77</v>
+        <v>22366.73</v>
       </c>
       <c r="J49" t="n">
         <v>189.94</v>
@@ -12883,7 +12883,7 @@
         <v>286.36</v>
       </c>
       <c r="I50" t="n">
-        <v>78184.3</v>
+        <v>78184.14999999999</v>
       </c>
       <c r="J50" t="n">
         <v>328.7</v>
@@ -12941,7 +12941,7 @@
         <v>286.36</v>
       </c>
       <c r="I51" t="n">
-        <v>32075.61</v>
+        <v>32075.55</v>
       </c>
       <c r="J51" t="n">
         <v>328.88</v>
@@ -12999,7 +12999,7 @@
         <v>308.74</v>
       </c>
       <c r="I52" t="n">
-        <v>17290.76</v>
+        <v>17290.73</v>
       </c>
       <c r="J52" t="n">
         <v>369.95</v>
@@ -13057,7 +13057,7 @@
         <v>286.36</v>
       </c>
       <c r="I53" t="n">
-        <v>41096.88</v>
+        <v>41096.8</v>
       </c>
       <c r="J53" t="n">
         <v>215.37</v>
@@ -13115,7 +13115,7 @@
         <v>308.74</v>
       </c>
       <c r="I54" t="n">
-        <v>25936.15</v>
+        <v>25936.1</v>
       </c>
       <c r="J54" t="n">
         <v>445.5</v>
@@ -13173,7 +13173,7 @@
         <v>348.06</v>
       </c>
       <c r="I55" t="n">
-        <v>81627.58</v>
+        <v>81627.44</v>
       </c>
       <c r="J55" t="n">
         <v>357.34</v>
@@ -13231,7 +13231,7 @@
         <v>348.06</v>
       </c>
       <c r="I56" t="n">
-        <v>63352.75</v>
+        <v>63352.64</v>
       </c>
       <c r="J56" t="n">
         <v>513.78</v>
@@ -13289,7 +13289,7 @@
         <v>348.06</v>
       </c>
       <c r="I57" t="n">
-        <v>53606.17</v>
+        <v>53606.08</v>
       </c>
       <c r="J57" t="n">
         <v>577.77</v>
@@ -13347,7 +13347,7 @@
         <v>348.06</v>
       </c>
       <c r="I58" t="n">
-        <v>21929.8</v>
+        <v>21929.76</v>
       </c>
       <c r="J58" t="n">
         <v>447.68</v>
@@ -13405,7 +13405,7 @@
         <v>348.06</v>
       </c>
       <c r="I59" t="n">
-        <v>8528.25</v>
+        <v>8528.24</v>
       </c>
       <c r="J59" t="n">
         <v>267.72</v>
@@ -13463,7 +13463,7 @@
         <v>348.06</v>
       </c>
       <c r="I60" t="n">
-        <v>19493.15</v>
+        <v>19493.12</v>
       </c>
       <c r="J60" t="n">
         <v>370.08</v>
@@ -13515,13 +13515,13 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>587.5544</v>
+        <v>588.0504</v>
       </c>
       <c r="H61" t="n">
         <v>55.64</v>
       </c>
       <c r="I61" t="n">
-        <v>32691.99</v>
+        <v>32716.97</v>
       </c>
       <c r="J61" t="n">
         <v>4.28</v>
@@ -13570,10 +13570,10 @@
         <v>462.0396</v>
       </c>
       <c r="H62" t="n">
-        <v>60.04</v>
+        <v>60.03</v>
       </c>
       <c r="I62" t="n">
-        <v>27738.74</v>
+        <v>27738.47</v>
       </c>
       <c r="J62" t="n">
         <v>13.54</v>
@@ -13625,7 +13625,7 @@
         <v>54.32</v>
       </c>
       <c r="I63" t="n">
-        <v>11598.56</v>
+        <v>11598.44</v>
       </c>
       <c r="J63" t="n">
         <v>1.51</v>
@@ -13677,7 +13677,7 @@
         <v>56.12</v>
       </c>
       <c r="I64" t="n">
-        <v>10606.96</v>
+        <v>10606.85</v>
       </c>
       <c r="J64" t="n">
         <v>5.29</v>
@@ -13729,7 +13729,7 @@
         <v>58.93</v>
       </c>
       <c r="I65" t="n">
-        <v>7838.18</v>
+        <v>7838.11</v>
       </c>
       <c r="J65" t="n">
         <v>11.21</v>
@@ -13781,7 +13781,7 @@
         <v>110.15</v>
       </c>
       <c r="I66" t="n">
-        <v>18120.56</v>
+        <v>18120.47</v>
       </c>
       <c r="J66" t="n">
         <v>103.3</v>
@@ -13833,7 +13833,7 @@
         <v>171.81</v>
       </c>
       <c r="I67" t="n">
-        <v>25258.54</v>
+        <v>25258.46</v>
       </c>
       <c r="J67" t="n">
         <v>171.76</v>
@@ -13885,7 +13885,7 @@
         <v>187.28</v>
       </c>
       <c r="I68" t="n">
-        <v>12455.07</v>
+        <v>12455.04</v>
       </c>
       <c r="J68" t="n">
         <v>218.82</v>
@@ -13937,7 +13937,7 @@
         <v>152.79</v>
       </c>
       <c r="I69" t="n">
-        <v>20322.3</v>
+        <v>20322.22</v>
       </c>
       <c r="J69" t="n">
         <v>183.69</v>
@@ -13989,7 +13989,7 @@
         <v>141.81</v>
       </c>
       <c r="I70" t="n">
-        <v>7941.95</v>
+        <v>7941.92</v>
       </c>
       <c r="J70" t="n">
         <v>125.96</v>
@@ -14041,7 +14041,7 @@
         <v>231.01</v>
       </c>
       <c r="I71" t="n">
-        <v>46899.45</v>
+        <v>46899.34</v>
       </c>
       <c r="J71" t="n">
         <v>331.17</v>
@@ -14093,7 +14093,7 @@
         <v>240.29</v>
       </c>
       <c r="I72" t="n">
-        <v>20186.1</v>
+        <v>20186.05</v>
       </c>
       <c r="J72" t="n">
         <v>276.29</v>
@@ -14139,13 +14139,13 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>656.3203999999999</v>
+        <v>658.0564000000001</v>
       </c>
       <c r="H73" t="n">
-        <v>105.37</v>
+        <v>105.36</v>
       </c>
       <c r="I73" t="n">
-        <v>69156.57000000001</v>
+        <v>69331.11</v>
       </c>
       <c r="J73" t="n">
         <v>1.06</v>
@@ -14197,7 +14197,7 @@
         <v>162.73</v>
       </c>
       <c r="I74" t="n">
-        <v>30758.9</v>
+        <v>30758.79</v>
       </c>
       <c r="J74" t="n">
         <v>113.39</v>
@@ -14249,7 +14249,7 @@
         <v>185.55</v>
       </c>
       <c r="I75" t="n">
-        <v>20134.38</v>
+        <v>20134.32</v>
       </c>
       <c r="J75" t="n">
         <v>129.6</v>
@@ -14301,7 +14301,7 @@
         <v>232.99</v>
       </c>
       <c r="I76" t="n">
-        <v>29359.15</v>
+        <v>29359.08</v>
       </c>
       <c r="J76" t="n">
         <v>209.49</v>
@@ -14353,7 +14353,7 @@
         <v>156.71</v>
       </c>
       <c r="I77" t="n">
-        <v>12616.57</v>
+        <v>12616.52</v>
       </c>
       <c r="J77" t="n">
         <v>101.42</v>
@@ -14405,7 +14405,7 @@
         <v>137.04</v>
       </c>
       <c r="I78" t="n">
-        <v>46050.4</v>
+        <v>46050.21</v>
       </c>
       <c r="J78" t="n">
         <v>1.39</v>
@@ -14457,7 +14457,7 @@
         <v>274.92</v>
       </c>
       <c r="I79" t="n">
-        <v>39454.23</v>
+        <v>39454.15</v>
       </c>
       <c r="J79" t="n">
         <v>202.79</v>
@@ -14509,7 +14509,7 @@
         <v>228.9</v>
       </c>
       <c r="I80" t="n">
-        <v>22434.55</v>
+        <v>22434.49</v>
       </c>
       <c r="J80" t="n">
         <v>132.55</v>
@@ -14561,7 +14561,7 @@
         <v>203.25</v>
       </c>
       <c r="I81" t="n">
-        <v>51222.52</v>
+        <v>51222.24</v>
       </c>
       <c r="J81" t="n">
         <v>122.66</v>
@@ -14613,7 +14613,7 @@
         <v>182.26</v>
       </c>
       <c r="I82" t="n">
-        <v>30622.9</v>
+        <v>30622.71</v>
       </c>
       <c r="J82" t="n">
         <v>80.92</v>
@@ -14665,7 +14665,7 @@
         <v>243.18</v>
       </c>
       <c r="I83" t="n">
-        <v>32346</v>
+        <v>32345.85</v>
       </c>
       <c r="J83" t="n">
         <v>166.27</v>
@@ -14717,7 +14717,7 @@
         <v>279.19</v>
       </c>
       <c r="I84" t="n">
-        <v>40066.79</v>
+        <v>40066.63</v>
       </c>
       <c r="J84" t="n">
         <v>226.91</v>
@@ -14769,7 +14769,7 @@
         <v>212.62</v>
       </c>
       <c r="I85" t="n">
-        <v>21582.97</v>
+        <v>21582.85</v>
       </c>
       <c r="J85" t="n">
         <v>114.8</v>
@@ -14821,7 +14821,7 @@
         <v>227.61</v>
       </c>
       <c r="I86" t="n">
-        <v>25494.96</v>
+        <v>25494.83</v>
       </c>
       <c r="J86" t="n">
         <v>140.05</v>
@@ -14873,7 +14873,7 @@
         <v>292.73</v>
       </c>
       <c r="I87" t="n">
-        <v>86070.17999999999</v>
+        <v>86069.84</v>
       </c>
       <c r="J87" t="n">
         <v>249.72</v>
@@ -14925,7 +14925,7 @@
         <v>318.72</v>
       </c>
       <c r="I88" t="n">
-        <v>47972.22</v>
+        <v>47972.05</v>
       </c>
       <c r="J88" t="n">
         <v>293.5</v>
@@ -14977,7 +14977,7 @@
         <v>305.59</v>
       </c>
       <c r="I89" t="n">
-        <v>33159.49</v>
+        <v>33159.37</v>
       </c>
       <c r="J89" t="n">
         <v>271.38</v>
@@ -15029,7 +15029,7 @@
         <v>264.97</v>
       </c>
       <c r="I90" t="n">
-        <v>25041.51</v>
+        <v>25041.41</v>
       </c>
       <c r="J90" t="n">
         <v>202.96</v>
@@ -15081,7 +15081,7 @@
         <v>205.33</v>
       </c>
       <c r="I91" t="n">
-        <v>56778</v>
+        <v>56777.68</v>
       </c>
       <c r="J91" t="n">
         <v>126.8</v>
@@ -15133,7 +15133,7 @@
         <v>190.78</v>
       </c>
       <c r="I92" t="n">
-        <v>29382.55</v>
+        <v>29382.37</v>
       </c>
       <c r="J92" t="n">
         <v>97.86</v>
@@ -15185,7 +15185,7 @@
         <v>220.64</v>
       </c>
       <c r="I93" t="n">
-        <v>27803.45</v>
+        <v>27803.31</v>
       </c>
       <c r="J93" t="n">
         <v>128.31</v>
@@ -15237,7 +15237,7 @@
         <v>244.11</v>
       </c>
       <c r="I94" t="n">
-        <v>33324.47</v>
+        <v>33324.31</v>
       </c>
       <c r="J94" t="n">
         <v>167.84</v>
@@ -15289,7 +15289,7 @@
         <v>239.51</v>
       </c>
       <c r="I95" t="n">
-        <v>19281.95</v>
+        <v>19281.86</v>
       </c>
       <c r="J95" t="n">
         <v>160.08</v>
@@ -15341,7 +15341,7 @@
         <v>203.13</v>
       </c>
       <c r="I96" t="n">
-        <v>19908.23</v>
+        <v>19908.12</v>
       </c>
       <c r="J96" t="n">
         <v>98.81</v>
@@ -15393,7 +15393,7 @@
         <v>141.86</v>
       </c>
       <c r="I97" t="n">
-        <v>55613.44</v>
+        <v>55613</v>
       </c>
       <c r="J97" t="n">
         <v>2.42</v>
@@ -15445,7 +15445,7 @@
         <v>178.01</v>
       </c>
       <c r="I98" t="n">
-        <v>21185.26</v>
+        <v>21185.13</v>
       </c>
       <c r="J98" t="n">
         <v>56.51</v>
@@ -15497,7 +15497,7 @@
         <v>182.48</v>
       </c>
       <c r="I99" t="n">
-        <v>19801.11</v>
+        <v>19800.99</v>
       </c>
       <c r="J99" t="n">
         <v>64.04000000000001</v>
@@ -15549,7 +15549,7 @@
         <v>165.45</v>
       </c>
       <c r="I100" t="n">
-        <v>12741.08</v>
+        <v>12740.99</v>
       </c>
       <c r="J100" t="n">
         <v>35.36</v>
@@ -15601,7 +15601,7 @@
         <v>156.29</v>
       </c>
       <c r="I101" t="n">
-        <v>14223.48</v>
+        <v>14223.38</v>
       </c>
       <c r="J101" t="n">
         <v>29.25</v>
@@ -15653,7 +15653,7 @@
         <v>183.23</v>
       </c>
       <c r="I102" t="n">
-        <v>37199.64</v>
+        <v>37199.41</v>
       </c>
       <c r="J102" t="n">
         <v>82.84999999999999</v>
@@ -15705,7 +15705,7 @@
         <v>178.57</v>
       </c>
       <c r="I103" t="n">
-        <v>25626.79</v>
+        <v>25626.63</v>
       </c>
       <c r="J103" t="n">
         <v>73.56999999999999</v>
@@ -15757,7 +15757,7 @@
         <v>175.03</v>
       </c>
       <c r="I104" t="n">
-        <v>28794.83</v>
+        <v>28794.64</v>
       </c>
       <c r="J104" t="n">
         <v>66.53</v>
@@ -15809,7 +15809,7 @@
         <v>203.11</v>
       </c>
       <c r="I105" t="n">
-        <v>17062.7</v>
+        <v>17062.61</v>
       </c>
       <c r="J105" t="n">
         <v>98.78</v>
@@ -15858,10 +15858,10 @@
         <v>259.0222</v>
       </c>
       <c r="H106" t="n">
-        <v>214.15</v>
+        <v>214.14</v>
       </c>
       <c r="I106" t="n">
-        <v>55468.38</v>
+        <v>55468.09</v>
       </c>
       <c r="J106" t="n">
         <v>144.34</v>
@@ -15913,7 +15913,7 @@
         <v>197.61</v>
       </c>
       <c r="I107" t="n">
-        <v>31818.13</v>
+        <v>31817.95</v>
       </c>
       <c r="J107" t="n">
         <v>111.45</v>
@@ -15965,7 +15965,7 @@
         <v>225.24</v>
       </c>
       <c r="I108" t="n">
-        <v>26018.03</v>
+        <v>26017.89</v>
       </c>
       <c r="J108" t="n">
         <v>136.06</v>
@@ -16017,7 +16017,7 @@
         <v>231.27</v>
       </c>
       <c r="I109" t="n">
-        <v>23475.67</v>
+        <v>23475.55</v>
       </c>
       <c r="J109" t="n">
         <v>178.4</v>
@@ -16069,7 +16069,7 @@
         <v>235.64</v>
       </c>
       <c r="I110" t="n">
-        <v>20620.4</v>
+        <v>20620.3</v>
       </c>
       <c r="J110" t="n">
         <v>153.57</v>
@@ -16115,13 +16115,13 @@
         </is>
       </c>
       <c r="G111" t="n">
-        <v>378.1564</v>
+        <v>378.0324</v>
       </c>
       <c r="H111" t="n">
         <v>274.06</v>
       </c>
       <c r="I111" t="n">
-        <v>103637.48</v>
+        <v>103603.85</v>
       </c>
       <c r="J111" t="n">
         <v>334.85</v>
@@ -16173,7 +16173,7 @@
         <v>223.15</v>
       </c>
       <c r="I112" t="n">
-        <v>48427.06</v>
+        <v>48426.94</v>
       </c>
       <c r="J112" t="n">
         <v>233.57</v>
@@ -16225,7 +16225,7 @@
         <v>276.18</v>
       </c>
       <c r="I113" t="n">
-        <v>32868.77</v>
+        <v>32868.7</v>
       </c>
       <c r="J113" t="n">
         <v>282.24</v>
@@ -16277,7 +16277,7 @@
         <v>319.43</v>
       </c>
       <c r="I114" t="n">
-        <v>34660.83</v>
+        <v>34660.77</v>
       </c>
       <c r="J114" t="n">
         <v>355.07</v>
@@ -16326,10 +16326,10 @@
         <v>98.00839999999999</v>
       </c>
       <c r="H115" t="n">
-        <v>279.14</v>
+        <v>279.13</v>
       </c>
       <c r="I115" t="n">
-        <v>27357.61</v>
+        <v>27357.56</v>
       </c>
       <c r="J115" t="n">
         <v>287.21</v>
@@ -16381,7 +16381,7 @@
         <v>186.13</v>
       </c>
       <c r="I116" t="n">
-        <v>59940.49</v>
+        <v>59940.31</v>
       </c>
       <c r="J116" t="n">
         <v>31.5</v>
@@ -16433,7 +16433,7 @@
         <v>168.32</v>
       </c>
       <c r="I117" t="n">
-        <v>35938.92</v>
+        <v>35938.8</v>
       </c>
       <c r="J117" t="n">
         <v>1.35</v>
@@ -16485,7 +16485,7 @@
         <v>188.79</v>
       </c>
       <c r="I118" t="n">
-        <v>25110.79</v>
+        <v>25110.71</v>
       </c>
       <c r="J118" t="n">
         <v>36.5</v>
@@ -16537,7 +16537,7 @@
         <v>180.02</v>
       </c>
       <c r="I119" t="n">
-        <v>13232.92</v>
+        <v>13232.87</v>
       </c>
       <c r="J119" t="n">
         <v>19.98</v>
@@ -16651,16 +16651,16 @@
         <v>1034000</v>
       </c>
       <c r="D5" t="n">
-        <v>3617.1</v>
+        <v>3619.3</v>
       </c>
       <c r="E5" t="n">
-        <v>3617.1</v>
+        <v>3619.3</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>1578421.23</v>
+        <v>1579191.07</v>
       </c>
       <c r="H5" t="n">
         <v>1.53</v>
@@ -16691,7 +16691,7 @@
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>1738789.86</v>
+        <v>1738652.09</v>
       </c>
       <c r="H6" t="n">
         <v>1.88</v>
@@ -16722,7 +16722,7 @@
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>1890887.36</v>
+        <v>1890739.04</v>
       </c>
       <c r="H7" t="n">
         <v>1.9</v>
@@ -16744,19 +16744,19 @@
         <v>967500</v>
       </c>
       <c r="D8" t="n">
-        <v>3386.7</v>
+        <v>3386.5</v>
       </c>
       <c r="E8" t="n">
-        <v>3386.7</v>
+        <v>3386.5</v>
       </c>
       <c r="F8" t="n">
         <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>2104441.25</v>
+        <v>2104224.23</v>
       </c>
       <c r="H8" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="I8" t="n">
         <v>0.3065</v>
@@ -16784,7 +16784,7 @@
         <v>0.7766</v>
       </c>
       <c r="G9" t="n">
-        <v>1743108.76</v>
+        <v>1742997.01</v>
       </c>
       <c r="H9" t="n">
         <v>1.79</v>
@@ -16829,7 +16829,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>One-off cost 0 PGK · annual change -6,213,500 PGK · payback n/a years</t>
+          <t>One-off cost 0 PGK · annual change -2,188,375 PGK · payback n/a years</t>
         </is>
       </c>
     </row>

--- a/docs/app/api/files/results-2.xlsx
+++ b/docs/app/api/files/results-2.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -516,7 +516,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-28 18:35 UTC · 53 ms</t>
+          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-28 19:24 UTC · 143 ms</t>
         </is>
       </c>
     </row>
@@ -798,6 +798,157 @@
       <c r="E16" t="inlineStr">
         <is>
           <t>flat</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Share of demand volume that is estimated</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Facilities with estimated demand</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>134</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Total annual cost with estimates 30% lower</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>7929062.41</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Fill rate (volume) with estimates 30% lower</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0.9556</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Fill rate, most vulnerable quintile with estimates 30% lower</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0.7766</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Hubs open with estimates 30% lower</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>5</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Total annual cost with estimates 30% higher</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>10089594.22</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fill rate (volume) with estimates 30% higher</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>0.9415</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Fill rate, most vulnerable quintile with estimates 30% higher</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>0.7649</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Hubs open with estimates 30% higher</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>5</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>count</t>
         </is>
       </c>
     </row>

--- a/docs/app/api/files/results-2.xlsx
+++ b/docs/app/api/files/results-2.xlsx
@@ -516,7 +516,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-28 19:24 UTC · 143 ms</t>
+          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-28 19:50 UTC · 62 ms</t>
         </is>
       </c>
     </row>

--- a/docs/app/api/files/results-2.xlsx
+++ b/docs/app/api/files/results-2.xlsx
@@ -516,7 +516,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-28 19:50 UTC · 62 ms</t>
+          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-28 22:36 UTC · 51 ms</t>
         </is>
       </c>
     </row>

--- a/docs/app/api/files/results-2.xlsx
+++ b/docs/app/api/files/results-2.xlsx
@@ -516,7 +516,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-28 22:36 UTC · 51 ms</t>
+          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-28 22:48 UTC · 47 ms</t>
         </is>
       </c>
     </row>

--- a/docs/app/api/files/results-2.xlsx
+++ b/docs/app/api/files/results-2.xlsx
@@ -516,7 +516,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-28 22:48 UTC · 47 ms</t>
+          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-28 22:57 UTC · 53 ms</t>
         </is>
       </c>
     </row>

--- a/docs/app/api/files/results-2.xlsx
+++ b/docs/app/api/files/results-2.xlsx
@@ -516,7 +516,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-28 22:57 UTC · 53 ms</t>
+          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-29 09:08 UTC · 70 ms</t>
         </is>
       </c>
     </row>

--- a/docs/app/api/files/results-2.xlsx
+++ b/docs/app/api/files/results-2.xlsx
@@ -516,7 +516,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-29 09:08 UTC · 70 ms</t>
+          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-29 09:19 UTC · 62 ms</t>
         </is>
       </c>
     </row>

--- a/docs/app/api/files/results-2.xlsx
+++ b/docs/app/api/files/results-2.xlsx
@@ -516,7 +516,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-29 09:19 UTC · 62 ms</t>
+          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-29 09:28 UTC · 71 ms</t>
         </is>
       </c>
     </row>

--- a/docs/app/api/files/results-2.xlsx
+++ b/docs/app/api/files/results-2.xlsx
@@ -516,7 +516,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-29 09:28 UTC · 71 ms</t>
+          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-29 09:40 UTC · 69 ms</t>
         </is>
       </c>
     </row>

--- a/docs/app/api/files/results-2.xlsx
+++ b/docs/app/api/files/results-2.xlsx
@@ -516,7 +516,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-29 09:40 UTC · 69 ms</t>
+          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-30 15:56 UTC · 127 ms</t>
         </is>
       </c>
     </row>

--- a/docs/app/api/files/results-2.xlsx
+++ b/docs/app/api/files/results-2.xlsx
@@ -516,7 +516,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-09-30 15:56 UTC · 127 ms</t>
+          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-10-06 14:14 UTC · 48 ms</t>
         </is>
       </c>
     </row>

--- a/docs/app/api/files/results-2.xlsx
+++ b/docs/app/api/files/results-2.xlsx
@@ -516,7 +516,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-10-06 14:14 UTC · 48 ms</t>
+          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-10-06 15:06 UTC · 48 ms</t>
         </is>
       </c>
     </row>

--- a/docs/app/api/files/results-2.xlsx
+++ b/docs/app/api/files/results-2.xlsx
@@ -516,7 +516,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-10-06 15:06 UTC · 48 ms</t>
+          <t>Conditions: Annualised · solver HiGHS Optimal · run 2026-10-06 15:14 UTC · 50 ms</t>
         </is>
       </c>
     </row>
